--- a/data/quarterly/FY26Q2.xlsx
+++ b/data/quarterly/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E89D6D7-7DC1-8342-A9AE-28713FCD6FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE5153-9DA8-AD4E-9EFD-EC02B1CCAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14260" yWindow="700" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="3360" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="44">
   <si>
     <t>總計</t>
   </si>
@@ -220,6 +220,14 @@
   </si>
   <si>
     <t>03/01-03/07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/08~03/14</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +559,12 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1069,7 +1082,11 @@
       </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
-      <c r="CC1" s="26"/>
+      <c r="CC1" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="CD1" s="26"/>
+      <c r="CF1" s="25"/>
       <c r="CK1" s="26"/>
       <c r="CS1" s="26"/>
     </row>
@@ -1136,7 +1153,9 @@
       <c r="BY2" s="21"/>
       <c r="BZ2" s="21"/>
       <c r="CA2" s="21"/>
-      <c r="CC2" s="22"/>
+      <c r="CC2" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="CD2" s="21"/>
       <c r="CF2" s="21"/>
       <c r="CG2" s="21"/>
@@ -1185,86 +1204,216 @@
       <c r="G4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="17"/>
-      <c r="AC4" s="16"/>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="16"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="17"/>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="16"/>
+      <c r="I4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="AO4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AP4" s="19"/>
-      <c r="AQ4" s="18"/>
-      <c r="AR4" s="17"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="16"/>
-      <c r="AU4" s="16"/>
+      <c r="AP4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="AW4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AX4" s="19"/>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="17"/>
-      <c r="BA4" s="16"/>
-      <c r="BB4" s="16"/>
-      <c r="BC4" s="16"/>
+      <c r="AX4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BA4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BE4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BF4" s="19"/>
-      <c r="BG4" s="18"/>
-      <c r="BH4" s="17"/>
-      <c r="BI4" s="16"/>
-      <c r="BJ4" s="16"/>
-      <c r="BK4" s="16"/>
+      <c r="BF4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BG4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BH4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BI4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BM4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BN4" s="19"/>
-      <c r="BO4" s="18"/>
-      <c r="BP4" s="17"/>
-      <c r="BQ4" s="16"/>
-      <c r="BR4" s="16"/>
-      <c r="BS4" s="16"/>
+      <c r="BN4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BP4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BR4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BU4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BV4" s="19"/>
-      <c r="BW4" s="18"/>
-      <c r="BX4" s="17"/>
-      <c r="BY4" s="16"/>
-      <c r="BZ4" s="16"/>
-      <c r="CA4" s="16"/>
-      <c r="CC4" s="19"/>
-      <c r="CD4" s="19"/>
-      <c r="CE4" s="18"/>
-      <c r="CF4" s="17"/>
-      <c r="CG4" s="16"/>
-      <c r="CH4" s="16"/>
-      <c r="CI4" s="16"/>
+      <c r="BV4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BX4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BY4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CC4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CD4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CE4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="CK4" s="19"/>
       <c r="CL4" s="19"/>
       <c r="CM4" s="18"/>
@@ -1502,13 +1651,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CB5" s="38"/>
-      <c r="CC5" s="14"/>
-      <c r="CD5" s="32"/>
-      <c r="CE5" s="15"/>
+      <c r="CC5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CD5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE5" s="15">
+        <v>6486</v>
+      </c>
       <c r="CF5" s="33"/>
-      <c r="CG5" s="10"/>
-      <c r="CH5" s="12"/>
-      <c r="CI5" s="11"/>
+      <c r="CG5" s="10">
+        <f t="shared" ref="CG5:CG65" si="23">CE5-BW5</f>
+        <v>1051</v>
+      </c>
+      <c r="CH5" s="12">
+        <f t="shared" ref="CH5:CH65" si="24">CF5-BX5</f>
+        <v>0</v>
+      </c>
+      <c r="CI5" s="11" t="e">
+        <f t="shared" ref="CI5:CI65" si="25">(CF5-BX5)/BX5</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CJ5" s="38"/>
       <c r="CK5" s="14"/>
       <c r="CL5" s="32"/>
@@ -1718,11 +1882,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC6" s="14"/>
-      <c r="CD6" s="32"/>
+      <c r="CD6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CF6" s="33"/>
-      <c r="CG6" s="10"/>
-      <c r="CH6" s="12"/>
-      <c r="CI6" s="11"/>
+      <c r="CG6" s="10">
+        <f t="shared" si="23"/>
+        <v>-13</v>
+      </c>
+      <c r="CH6" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI6" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK6" s="14"/>
       <c r="CL6" s="32"/>
       <c r="CN6" s="33"/>
@@ -1948,10 +2123,27 @@
         <v>-0.20274549452624313</v>
       </c>
       <c r="CC7" s="14"/>
-      <c r="CD7" s="13"/>
-      <c r="CF7" s="12"/>
-      <c r="CH7" s="12"/>
-      <c r="CI7" s="11"/>
+      <c r="CD7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE7" s="10">
+        <v>186</v>
+      </c>
+      <c r="CF7" s="12">
+        <v>218509.52380868993</v>
+      </c>
+      <c r="CG7" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="CH7" s="12">
+        <f t="shared" si="24"/>
+        <v>-9042.8571429600124</v>
+      </c>
+      <c r="CI7" s="11">
+        <f t="shared" si="25"/>
+        <v>-3.9739672708067282E-2</v>
+      </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13"/>
       <c r="CN7" s="12"/>
@@ -2175,10 +2367,27 @@
         <v>-0.33201301486241308</v>
       </c>
       <c r="CC8" s="14"/>
-      <c r="CD8" s="13"/>
-      <c r="CF8" s="12"/>
-      <c r="CH8" s="12"/>
-      <c r="CI8" s="11"/>
+      <c r="CD8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE8" s="10">
+        <v>233</v>
+      </c>
+      <c r="CF8" s="12">
+        <v>280382.85714268993</v>
+      </c>
+      <c r="CG8" s="10">
+        <f t="shared" si="23"/>
+        <v>-18</v>
+      </c>
+      <c r="CH8" s="12">
+        <f t="shared" si="24"/>
+        <v>-28153.333333340066</v>
+      </c>
+      <c r="CI8" s="11">
+        <f t="shared" si="25"/>
+        <v>-9.1248074625875322E-2</v>
+      </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13"/>
       <c r="CN8" s="12"/>
@@ -2402,10 +2611,27 @@
         <v>-0.35691653359845976</v>
       </c>
       <c r="CC9" s="14"/>
-      <c r="CD9" s="13"/>
-      <c r="CF9" s="12"/>
-      <c r="CH9" s="12"/>
-      <c r="CI9" s="11"/>
+      <c r="CD9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE9" s="10">
+        <v>75</v>
+      </c>
+      <c r="CF9" s="12">
+        <v>497857.14285712998</v>
+      </c>
+      <c r="CG9" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH9" s="12">
+        <f t="shared" si="24"/>
+        <v>9980.9523809599923</v>
+      </c>
+      <c r="CI9" s="11">
+        <f t="shared" si="25"/>
+        <v>2.0457961621817462E-2</v>
+      </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13"/>
       <c r="CN9" s="12"/>
@@ -2629,10 +2855,27 @@
         <v>-0.51457530616739655</v>
       </c>
       <c r="CC10" s="14"/>
-      <c r="CD10" s="13"/>
-      <c r="CF10" s="12"/>
-      <c r="CH10" s="12"/>
-      <c r="CI10" s="11"/>
+      <c r="CD10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE10" s="10">
+        <v>39</v>
+      </c>
+      <c r="CF10" s="12">
+        <v>521999.99999993003</v>
+      </c>
+      <c r="CG10" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH10" s="12">
+        <f t="shared" si="24"/>
+        <v>62095.238095240027</v>
+      </c>
+      <c r="CI10" s="11">
+        <f t="shared" si="25"/>
+        <v>0.13501760198801455</v>
+      </c>
       <c r="CK10" s="14"/>
       <c r="CL10" s="13"/>
       <c r="CN10" s="12"/>
@@ -2836,10 +3079,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC11" s="14"/>
-      <c r="CD11" s="13"/>
+      <c r="CD11" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF11" s="12"/>
-      <c r="CH11" s="12"/>
-      <c r="CI11" s="11"/>
+      <c r="CG11" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH11" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI11" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK11" s="14"/>
       <c r="CL11" s="13"/>
       <c r="CN11" s="12"/>
@@ -3063,10 +3318,27 @@
         <v>-6.9623271340009535E-2</v>
       </c>
       <c r="CC12" s="14"/>
-      <c r="CD12" s="13"/>
-      <c r="CF12" s="12"/>
-      <c r="CH12" s="12"/>
-      <c r="CI12" s="11"/>
+      <c r="CD12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE12" s="10">
+        <v>6</v>
+      </c>
+      <c r="CF12" s="12">
+        <v>36740</v>
+      </c>
+      <c r="CG12" s="10">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="CH12" s="12">
+        <f t="shared" si="24"/>
+        <v>-2280</v>
+      </c>
+      <c r="CI12" s="11">
+        <f t="shared" si="25"/>
+        <v>-5.84315735520246E-2</v>
+      </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13"/>
       <c r="CN12" s="12"/>
@@ -3290,10 +3562,27 @@
         <v>-0.54386964867508925</v>
       </c>
       <c r="CC13" s="14"/>
-      <c r="CD13" s="13"/>
-      <c r="CF13" s="12"/>
-      <c r="CH13" s="12"/>
-      <c r="CI13" s="11"/>
+      <c r="CD13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE13" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>689619.04761897994</v>
+      </c>
+      <c r="CG13" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="CH13" s="12">
+        <f t="shared" si="24"/>
+        <v>98947.619047599961</v>
+      </c>
+      <c r="CI13" s="11">
+        <f t="shared" si="25"/>
+        <v>0.16751719189620934</v>
+      </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13"/>
       <c r="CN13" s="12"/>
@@ -3517,10 +3806,27 @@
         <v>-0.44431372549018977</v>
       </c>
       <c r="CC14" s="14"/>
-      <c r="CD14" s="13"/>
-      <c r="CF14" s="12"/>
-      <c r="CH14" s="12"/>
-      <c r="CI14" s="11"/>
+      <c r="CD14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE14" s="10">
+        <v>43</v>
+      </c>
+      <c r="CF14" s="12">
+        <v>784380.95238087</v>
+      </c>
+      <c r="CG14" s="10">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="CH14" s="12">
+        <f t="shared" si="24"/>
+        <v>-25333.333333360031</v>
+      </c>
+      <c r="CI14" s="11">
+        <f t="shared" si="25"/>
+        <v>-3.1286756057433383E-2</v>
+      </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13"/>
       <c r="CN14" s="12"/>
@@ -3744,10 +4050,27 @@
         <v>-0.31319967528634601</v>
       </c>
       <c r="CC15" s="14"/>
-      <c r="CD15" s="13"/>
-      <c r="CF15" s="12"/>
-      <c r="CH15" s="12"/>
-      <c r="CI15" s="11"/>
+      <c r="CD15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE15" s="10">
+        <v>159</v>
+      </c>
+      <c r="CF15" s="12">
+        <v>6124231.4285713602</v>
+      </c>
+      <c r="CG15" s="10">
+        <f t="shared" si="23"/>
+        <v>94</v>
+      </c>
+      <c r="CH15" s="12">
+        <f t="shared" si="24"/>
+        <v>3714231.4285714002</v>
+      </c>
+      <c r="CI15" s="11">
+        <f t="shared" si="25"/>
+        <v>1.5411748666271627</v>
+      </c>
       <c r="CK15" s="14"/>
       <c r="CL15" s="13"/>
       <c r="CN15" s="12"/>
@@ -3971,13 +4294,28 @@
         <f t="shared" si="22"/>
         <v>-0.39093242952524898</v>
       </c>
-      <c r="CC16" s="9"/>
+      <c r="CC16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CD16" s="9"/>
-      <c r="CE16" s="8"/>
-      <c r="CF16" s="7"/>
-      <c r="CG16" s="27"/>
-      <c r="CH16" s="28"/>
-      <c r="CI16" s="29"/>
+      <c r="CE16" s="8">
+        <v>759</v>
+      </c>
+      <c r="CF16" s="7">
+        <v>9153720.9523796495</v>
+      </c>
+      <c r="CG16" s="27">
+        <f t="shared" si="23"/>
+        <v>70</v>
+      </c>
+      <c r="CH16" s="28">
+        <f t="shared" si="24"/>
+        <v>3820445.7142855395</v>
+      </c>
+      <c r="CI16" s="29">
+        <f t="shared" si="25"/>
+        <v>0.71634137443294743</v>
+      </c>
       <c r="CK16" s="9"/>
       <c r="CL16" s="9"/>
       <c r="CM16" s="8"/>
@@ -4204,13 +4542,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC17" s="14"/>
-      <c r="CD17" s="32"/>
-      <c r="CE17" s="15"/>
+      <c r="CC17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CD17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE17" s="15">
+        <v>5542</v>
+      </c>
       <c r="CF17" s="33"/>
-      <c r="CG17" s="10"/>
-      <c r="CH17" s="12"/>
-      <c r="CI17" s="11"/>
+      <c r="CG17" s="10">
+        <f t="shared" si="23"/>
+        <v>1518</v>
+      </c>
+      <c r="CH17" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI17" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK17" s="14"/>
       <c r="CL17" s="32"/>
       <c r="CM17" s="15"/>
@@ -4418,12 +4771,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC18" s="14"/>
-      <c r="CD18" s="32"/>
+      <c r="CD18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE18" s="15"/>
       <c r="CF18" s="33"/>
-      <c r="CG18" s="10"/>
-      <c r="CH18" s="12"/>
-      <c r="CI18" s="11"/>
+      <c r="CG18" s="10">
+        <f t="shared" si="23"/>
+        <v>-5</v>
+      </c>
+      <c r="CH18" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI18" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK18" s="14"/>
       <c r="CL18" s="32"/>
       <c r="CM18" s="15"/>
@@ -4651,10 +5015,27 @@
         <v>-0.34594286378034994</v>
       </c>
       <c r="CC19" s="14"/>
-      <c r="CD19" s="13"/>
-      <c r="CF19" s="12"/>
-      <c r="CH19" s="12"/>
-      <c r="CI19" s="11"/>
+      <c r="CD19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE19" s="10">
+        <v>204</v>
+      </c>
+      <c r="CF19" s="12">
+        <v>216177.14285634996</v>
+      </c>
+      <c r="CG19" s="10">
+        <f t="shared" si="23"/>
+        <v>84</v>
+      </c>
+      <c r="CH19" s="12">
+        <f t="shared" si="24"/>
+        <v>98193.333333059942</v>
+      </c>
+      <c r="CI19" s="11">
+        <f t="shared" si="25"/>
+        <v>0.83226108505740837</v>
+      </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13"/>
       <c r="CN19" s="12"/>
@@ -4878,10 +5259,27 @@
         <v>-0.203679873159022</v>
       </c>
       <c r="CC20" s="14"/>
-      <c r="CD20" s="13"/>
-      <c r="CF20" s="12"/>
-      <c r="CH20" s="12"/>
-      <c r="CI20" s="11"/>
+      <c r="CD20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE20" s="10">
+        <v>253</v>
+      </c>
+      <c r="CF20" s="12">
+        <v>306130.47619033</v>
+      </c>
+      <c r="CG20" s="10">
+        <f t="shared" si="23"/>
+        <v>42</v>
+      </c>
+      <c r="CH20" s="12">
+        <f t="shared" si="24"/>
+        <v>100448.57142858999</v>
+      </c>
+      <c r="CI20" s="11">
+        <f t="shared" si="25"/>
+        <v>0.48836853949280895</v>
+      </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13"/>
       <c r="CN20" s="12"/>
@@ -5105,10 +5503,27 @@
         <v>-6.0940078645477097E-2</v>
       </c>
       <c r="CC21" s="14"/>
-      <c r="CD21" s="13"/>
-      <c r="CF21" s="12"/>
-      <c r="CH21" s="12"/>
-      <c r="CI21" s="11"/>
+      <c r="CD21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE21" s="10">
+        <v>54</v>
+      </c>
+      <c r="CF21" s="12">
+        <v>328057.14285712002</v>
+      </c>
+      <c r="CG21" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="CH21" s="12">
+        <f t="shared" si="24"/>
+        <v>-110895.23809524998</v>
+      </c>
+      <c r="CI21" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.25263614666959294</v>
+      </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13"/>
       <c r="CN21" s="12"/>
@@ -5332,10 +5747,27 @@
         <v>-0.40599633411888447</v>
       </c>
       <c r="CC22" s="14"/>
-      <c r="CD22" s="13"/>
-      <c r="CF22" s="12"/>
-      <c r="CH22" s="12"/>
-      <c r="CI22" s="11"/>
+      <c r="CD22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE22" s="10">
+        <v>39</v>
+      </c>
+      <c r="CF22" s="12">
+        <v>483428.57142850995</v>
+      </c>
+      <c r="CG22" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH22" s="12">
+        <f t="shared" si="24"/>
+        <v>51333.333333329938</v>
+      </c>
+      <c r="CI22" s="11">
+        <f t="shared" si="25"/>
+        <v>0.11880096980384325</v>
+      </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13"/>
       <c r="CN22" s="12"/>
@@ -5549,10 +5981,27 @@
         <v>-1</v>
       </c>
       <c r="CC23" s="14"/>
-      <c r="CD23" s="13"/>
-      <c r="CF23" s="12"/>
-      <c r="CH23" s="12"/>
-      <c r="CI23" s="11"/>
+      <c r="CD23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CE23" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF23" s="12">
+        <v>11514.285714279999</v>
+      </c>
+      <c r="CG23" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH23" s="12">
+        <f t="shared" si="24"/>
+        <v>11514.285714279999</v>
+      </c>
+      <c r="CI23" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK23" s="14"/>
       <c r="CL23" s="13"/>
       <c r="CN23" s="12"/>
@@ -5776,10 +6225,27 @@
         <v>-0.16751824817518249</v>
       </c>
       <c r="CC24" s="14"/>
-      <c r="CD24" s="13"/>
-      <c r="CF24" s="12"/>
-      <c r="CH24" s="12"/>
-      <c r="CI24" s="11"/>
+      <c r="CD24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE24" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF24" s="12">
+        <v>104510</v>
+      </c>
+      <c r="CG24" s="10">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="CH24" s="12">
+        <f t="shared" si="24"/>
+        <v>58890</v>
+      </c>
+      <c r="CI24" s="11">
+        <f t="shared" si="25"/>
+        <v>1.2908811924594477</v>
+      </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13"/>
       <c r="CN24" s="12"/>
@@ -6003,10 +6469,27 @@
         <v>-0.40849879269777506</v>
       </c>
       <c r="CC25" s="14"/>
-      <c r="CD25" s="13"/>
-      <c r="CF25" s="12"/>
-      <c r="CH25" s="12"/>
-      <c r="CI25" s="11"/>
+      <c r="CD25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE25" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF25" s="12">
+        <v>336195.23809522</v>
+      </c>
+      <c r="CG25" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH25" s="12">
+        <f t="shared" si="24"/>
+        <v>153052.38095239</v>
+      </c>
+      <c r="CI25" s="11">
+        <f t="shared" si="25"/>
+        <v>0.83569942797729235</v>
+      </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13"/>
       <c r="CN25" s="12"/>
@@ -6230,10 +6713,27 @@
         <v>-0.43693446668496028</v>
       </c>
       <c r="CC26" s="14"/>
-      <c r="CD26" s="13"/>
-      <c r="CF26" s="12"/>
-      <c r="CH26" s="12"/>
-      <c r="CI26" s="11"/>
+      <c r="CD26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE26" s="10">
+        <v>34</v>
+      </c>
+      <c r="CF26" s="12">
+        <v>621619.04761897004</v>
+      </c>
+      <c r="CG26" s="10">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="CH26" s="12">
+        <f t="shared" si="24"/>
+        <v>230476.19047616003</v>
+      </c>
+      <c r="CI26" s="11">
+        <f t="shared" si="25"/>
+        <v>0.58923788653517695</v>
+      </c>
       <c r="CK26" s="14"/>
       <c r="CL26" s="13"/>
       <c r="CN26" s="12"/>
@@ -6457,10 +6957,27 @@
         <v>-0.55976195051904498</v>
       </c>
       <c r="CC27" s="14"/>
-      <c r="CD27" s="13"/>
-      <c r="CF27" s="12"/>
-      <c r="CH27" s="12"/>
-      <c r="CI27" s="11"/>
+      <c r="CD27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE27" s="10">
+        <v>145</v>
+      </c>
+      <c r="CF27" s="12">
+        <v>5108095.2380951494</v>
+      </c>
+      <c r="CG27" s="10">
+        <f t="shared" si="23"/>
+        <v>126</v>
+      </c>
+      <c r="CH27" s="12">
+        <f t="shared" si="24"/>
+        <v>4447047.6190475496</v>
+      </c>
+      <c r="CI27" s="11">
+        <f t="shared" si="25"/>
+        <v>6.7272727272728154</v>
+      </c>
       <c r="CK27" s="14"/>
       <c r="CL27" s="13"/>
       <c r="CN27" s="12"/>
@@ -6684,13 +7201,28 @@
         <f t="shared" si="22"/>
         <v>-0.41098482874390835</v>
       </c>
-      <c r="CC28" s="9"/>
+      <c r="CC28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CD28" s="9"/>
-      <c r="CE28" s="8"/>
-      <c r="CF28" s="7"/>
-      <c r="CG28" s="27"/>
-      <c r="CH28" s="28"/>
-      <c r="CI28" s="29"/>
+      <c r="CE28" s="8">
+        <v>759</v>
+      </c>
+      <c r="CF28" s="7">
+        <v>7515727.1428559292</v>
+      </c>
+      <c r="CG28" s="27">
+        <f t="shared" si="23"/>
+        <v>274</v>
+      </c>
+      <c r="CH28" s="28">
+        <f t="shared" si="24"/>
+        <v>5040060.4761901088</v>
+      </c>
+      <c r="CI28" s="29">
+        <f t="shared" si="25"/>
+        <v>2.0358396968594983</v>
+      </c>
       <c r="CK28" s="9"/>
       <c r="CL28" s="9"/>
       <c r="CM28" s="8"/>
@@ -6917,13 +7449,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC29" s="14"/>
-      <c r="CD29" s="32"/>
-      <c r="CE29" s="15"/>
+      <c r="CC29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CD29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE29" s="15">
+        <v>3502</v>
+      </c>
       <c r="CF29" s="33"/>
-      <c r="CG29" s="10"/>
-      <c r="CH29" s="12"/>
-      <c r="CI29" s="11"/>
+      <c r="CG29" s="10">
+        <f t="shared" si="23"/>
+        <v>754</v>
+      </c>
+      <c r="CH29" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI29" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK29" s="14"/>
       <c r="CL29" s="32"/>
       <c r="CM29" s="15"/>
@@ -7131,12 +7678,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC30" s="14"/>
-      <c r="CD30" s="32"/>
+      <c r="CD30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE30" s="15"/>
       <c r="CF30" s="33"/>
-      <c r="CG30" s="10"/>
-      <c r="CH30" s="12"/>
-      <c r="CI30" s="11"/>
+      <c r="CG30" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="CH30" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI30" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK30" s="14"/>
       <c r="CL30" s="32"/>
       <c r="CM30" s="15"/>
@@ -7364,10 +7922,27 @@
         <v>0.15327535985335874</v>
       </c>
       <c r="CC31" s="14"/>
-      <c r="CD31" s="13"/>
-      <c r="CF31" s="12"/>
-      <c r="CH31" s="12"/>
-      <c r="CI31" s="11"/>
+      <c r="CD31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE31" s="10">
+        <v>87</v>
+      </c>
+      <c r="CF31" s="12">
+        <v>76910.476190090034</v>
+      </c>
+      <c r="CG31" s="10">
+        <f t="shared" si="23"/>
+        <v>-14</v>
+      </c>
+      <c r="CH31" s="12">
+        <f t="shared" si="24"/>
+        <v>-26407.619047550004</v>
+      </c>
+      <c r="CI31" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.25559529515919094</v>
+      </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13"/>
       <c r="CN31" s="12"/>
@@ -7591,10 +8166,27 @@
         <v>-0.25161821315016214</v>
       </c>
       <c r="CC32" s="14"/>
-      <c r="CD32" s="13"/>
-      <c r="CF32" s="12"/>
-      <c r="CH32" s="12"/>
-      <c r="CI32" s="11"/>
+      <c r="CD32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE32" s="10">
+        <v>80</v>
+      </c>
+      <c r="CF32" s="12">
+        <v>83333.333333229995</v>
+      </c>
+      <c r="CG32" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH32" s="12">
+        <f t="shared" si="24"/>
+        <v>198.0952381100069</v>
+      </c>
+      <c r="CI32" s="11">
+        <f t="shared" si="25"/>
+        <v>2.382807130273138E-3</v>
+      </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13"/>
       <c r="CN32" s="12"/>
@@ -7818,10 +8410,27 @@
         <v>1.0662089720679766</v>
       </c>
       <c r="CC33" s="14"/>
-      <c r="CD33" s="13"/>
-      <c r="CF33" s="12"/>
-      <c r="CH33" s="12"/>
-      <c r="CI33" s="11"/>
+      <c r="CD33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE33" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF33" s="12">
+        <v>112676.19047618</v>
+      </c>
+      <c r="CG33" s="10">
+        <f t="shared" si="23"/>
+        <v>-11</v>
+      </c>
+      <c r="CH33" s="12">
+        <f t="shared" si="24"/>
+        <v>-96561.904761890008</v>
+      </c>
+      <c r="CI33" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.46149294492488274</v>
+      </c>
       <c r="CK33" s="14"/>
       <c r="CL33" s="13"/>
       <c r="CN33" s="12"/>
@@ -8045,10 +8654,27 @@
         <v>5.4496124031015132</v>
       </c>
       <c r="CC34" s="14"/>
-      <c r="CD34" s="13"/>
-      <c r="CF34" s="12"/>
-      <c r="CH34" s="12"/>
-      <c r="CI34" s="11"/>
+      <c r="CD34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE34" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF34" s="12">
+        <v>107238.09523807</v>
+      </c>
+      <c r="CG34" s="10">
+        <f t="shared" si="23"/>
+        <v>-10</v>
+      </c>
+      <c r="CH34" s="12">
+        <f t="shared" si="24"/>
+        <v>-130476.19047616003</v>
+      </c>
+      <c r="CI34" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.54887820512820562</v>
+      </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13"/>
       <c r="CN34" s="12"/>
@@ -8252,10 +8878,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC35" s="14"/>
-      <c r="CD35" s="13"/>
-      <c r="CF35" s="12"/>
-      <c r="CH35" s="12"/>
-      <c r="CI35" s="11"/>
+      <c r="CD35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CE35" s="10">
+        <v>1</v>
+      </c>
+      <c r="CF35" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CG35" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH35" s="12">
+        <f t="shared" si="24"/>
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CI35" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK35" s="14"/>
       <c r="CL35" s="13"/>
       <c r="CN35" s="12"/>
@@ -8469,10 +9112,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC36" s="14"/>
-      <c r="CD36" s="13"/>
-      <c r="CF36" s="12"/>
-      <c r="CH36" s="12"/>
-      <c r="CI36" s="11"/>
+      <c r="CD36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE36" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF36" s="12">
+        <v>8480</v>
+      </c>
+      <c r="CG36" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH36" s="12">
+        <f t="shared" si="24"/>
+        <v>65.71428571999968</v>
+      </c>
+      <c r="CI36" s="11">
+        <f t="shared" si="25"/>
+        <v>7.8098471993261484E-3</v>
+      </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13"/>
       <c r="CN36" s="12"/>
@@ -8679,7 +9339,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="23">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="26">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -8691,10 +9351,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC37" s="14"/>
-      <c r="CD37" s="13"/>
-      <c r="CF37" s="12"/>
-      <c r="CH37" s="12"/>
-      <c r="CI37" s="11"/>
+      <c r="CD37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE37" s="10">
+        <v>3</v>
+      </c>
+      <c r="CF37" s="12">
+        <v>84454.285714270009</v>
+      </c>
+      <c r="CG37" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH37" s="12">
+        <f t="shared" si="24"/>
+        <v>58306.666666660007</v>
+      </c>
+      <c r="CI37" s="11">
+        <f t="shared" si="25"/>
+        <v>2.2299034784197485</v>
+      </c>
       <c r="CK37" s="14"/>
       <c r="CL37" s="13"/>
       <c r="CN37" s="12"/>
@@ -8906,7 +9583,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -8918,10 +9595,27 @@
         <v>-4.3709391612534981E-2</v>
       </c>
       <c r="CC38" s="14"/>
-      <c r="CD38" s="13"/>
-      <c r="CF38" s="12"/>
-      <c r="CH38" s="12"/>
-      <c r="CI38" s="11"/>
+      <c r="CD38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE38" s="10">
+        <v>11</v>
+      </c>
+      <c r="CF38" s="12">
+        <v>180285.71428568001</v>
+      </c>
+      <c r="CG38" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH38" s="12">
+        <f t="shared" si="24"/>
+        <v>26095.238095230015</v>
+      </c>
+      <c r="CI38" s="11">
+        <f t="shared" si="25"/>
+        <v>0.16924027177267556</v>
+      </c>
       <c r="CK38" s="14"/>
       <c r="CL38" s="13"/>
       <c r="CN38" s="12"/>
@@ -9133,7 +9827,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -9145,10 +9839,27 @@
         <v>0.45893157702160037</v>
       </c>
       <c r="CC39" s="14"/>
-      <c r="CD39" s="13"/>
-      <c r="CF39" s="12"/>
-      <c r="CH39" s="12"/>
-      <c r="CI39" s="11"/>
+      <c r="CD39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE39" s="10">
+        <v>15</v>
+      </c>
+      <c r="CF39" s="12">
+        <v>454761.90476189001</v>
+      </c>
+      <c r="CG39" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH39" s="12">
+        <f t="shared" si="24"/>
+        <v>75022.857142860012</v>
+      </c>
+      <c r="CI39" s="11">
+        <f t="shared" si="25"/>
+        <v>0.19756424211114065</v>
+      </c>
       <c r="CK39" s="14"/>
       <c r="CL39" s="13"/>
       <c r="CN39" s="12"/>
@@ -9361,7 +10072,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -9372,13 +10083,28 @@
         <f t="shared" si="22"/>
         <v>0.5807760381895346</v>
       </c>
-      <c r="CC40" s="9"/>
+      <c r="CC40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CD40" s="9"/>
-      <c r="CE40" s="8"/>
-      <c r="CF40" s="7"/>
-      <c r="CG40" s="27"/>
-      <c r="CH40" s="28"/>
-      <c r="CI40" s="29"/>
+      <c r="CE40" s="8">
+        <v>227</v>
+      </c>
+      <c r="CF40" s="7">
+        <v>1116997.1428565499</v>
+      </c>
+      <c r="CG40" s="27">
+        <f t="shared" si="23"/>
+        <v>-22</v>
+      </c>
+      <c r="CH40" s="28">
+        <f t="shared" si="24"/>
+        <v>-84899.999999880092</v>
+      </c>
+      <c r="CI40" s="29">
+        <f t="shared" si="25"/>
+        <v>-7.0638324173154007E-2</v>
+      </c>
       <c r="CK40" s="9"/>
       <c r="CL40" s="9"/>
       <c r="CM40" s="8"/>
@@ -9594,7 +10320,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -9605,13 +10331,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC41" s="14"/>
-      <c r="CD41" s="32"/>
-      <c r="CE41" s="15"/>
+      <c r="CC41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CD41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE41" s="15">
+        <v>1285</v>
+      </c>
       <c r="CF41" s="33"/>
-      <c r="CG41" s="10"/>
-      <c r="CH41" s="12"/>
-      <c r="CI41" s="11"/>
+      <c r="CG41" s="10">
+        <f t="shared" si="23"/>
+        <v>231</v>
+      </c>
+      <c r="CH41" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI41" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK41" s="14"/>
       <c r="CL41" s="32"/>
       <c r="CM41" s="15"/>
@@ -9807,7 +10548,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -9819,12 +10560,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC42" s="14"/>
-      <c r="CD42" s="32"/>
+      <c r="CD42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE42" s="15"/>
       <c r="CF42" s="33"/>
-      <c r="CG42" s="10"/>
-      <c r="CH42" s="12"/>
-      <c r="CI42" s="11"/>
+      <c r="CG42" s="10">
+        <f t="shared" si="23"/>
+        <v>-5</v>
+      </c>
+      <c r="CH42" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI42" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK42" s="14"/>
       <c r="CL42" s="32"/>
       <c r="CM42" s="15"/>
@@ -10040,7 +10792,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -10052,10 +10804,27 @@
         <v>-0.26155671044421785</v>
       </c>
       <c r="CC43" s="14"/>
-      <c r="CD43" s="13"/>
-      <c r="CF43" s="12"/>
-      <c r="CH43" s="12"/>
-      <c r="CI43" s="11"/>
+      <c r="CD43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE43" s="10">
+        <v>110</v>
+      </c>
+      <c r="CF43" s="12">
+        <v>85552.380951930012</v>
+      </c>
+      <c r="CG43" s="10">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="CH43" s="12">
+        <f t="shared" si="24"/>
+        <v>3139.9999998500134</v>
+      </c>
+      <c r="CI43" s="11">
+        <f t="shared" si="25"/>
+        <v>3.8101071265928071E-2</v>
+      </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13"/>
       <c r="CN43" s="12"/>
@@ -10267,7 +11036,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -10279,10 +11048,27 @@
         <v>0.18373829204542183</v>
       </c>
       <c r="CC44" s="14"/>
-      <c r="CD44" s="13"/>
-      <c r="CF44" s="12"/>
-      <c r="CH44" s="12"/>
-      <c r="CI44" s="11"/>
+      <c r="CD44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE44" s="10">
+        <v>88</v>
+      </c>
+      <c r="CF44" s="12">
+        <v>88811.428571319979</v>
+      </c>
+      <c r="CG44" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH44" s="12">
+        <f t="shared" si="24"/>
+        <v>-1340.9523809300154</v>
+      </c>
+      <c r="CI44" s="11">
+        <f t="shared" si="25"/>
+        <v>-1.4874286921387718E-2</v>
+      </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13"/>
       <c r="CN44" s="12"/>
@@ -10494,7 +11280,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -10506,10 +11292,27 @@
         <v>-0.11683599419452342</v>
       </c>
       <c r="CC45" s="14"/>
-      <c r="CD45" s="13"/>
-      <c r="CF45" s="12"/>
-      <c r="CH45" s="12"/>
-      <c r="CI45" s="11"/>
+      <c r="CD45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE45" s="10">
+        <v>21</v>
+      </c>
+      <c r="CF45" s="12">
+        <v>139443.80952379998</v>
+      </c>
+      <c r="CG45" s="10">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="CH45" s="12">
+        <f t="shared" si="24"/>
+        <v>46719.999999999971</v>
+      </c>
+      <c r="CI45" s="11">
+        <f t="shared" si="25"/>
+        <v>0.50386195562864633</v>
+      </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13"/>
       <c r="CN45" s="12"/>
@@ -10721,7 +11524,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -10733,10 +11536,27 @@
         <v>0.20370370370373575</v>
       </c>
       <c r="CC46" s="14"/>
-      <c r="CD46" s="13"/>
-      <c r="CF46" s="12"/>
-      <c r="CH46" s="12"/>
-      <c r="CI46" s="11"/>
+      <c r="CD46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE46" s="10">
+        <v>16</v>
+      </c>
+      <c r="CF46" s="12">
+        <v>186095.23809520004</v>
+      </c>
+      <c r="CG46" s="10">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="CH46" s="12">
+        <f t="shared" si="24"/>
+        <v>74666.666666660036</v>
+      </c>
+      <c r="CI46" s="11">
+        <f t="shared" si="25"/>
+        <v>0.6700854700855996</v>
+      </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13"/>
       <c r="CN46" s="12"/>
@@ -10928,7 +11748,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -10940,10 +11760,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC47" s="14"/>
-      <c r="CD47" s="13"/>
+      <c r="CD47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF47" s="12"/>
-      <c r="CH47" s="12"/>
-      <c r="CI47" s="11"/>
+      <c r="CG47" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH47" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI47" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK47" s="14"/>
       <c r="CL47" s="13"/>
       <c r="CN47" s="12"/>
@@ -11155,7 +11987,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -11167,10 +11999,27 @@
         <v>-0.35685071574642124</v>
       </c>
       <c r="CC48" s="14"/>
-      <c r="CD48" s="13"/>
-      <c r="CF48" s="12"/>
-      <c r="CH48" s="12"/>
-      <c r="CI48" s="11"/>
+      <c r="CD48" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE48" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF48" s="12">
+        <v>15380</v>
+      </c>
+      <c r="CG48" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH48" s="12">
+        <f t="shared" si="24"/>
+        <v>9090</v>
+      </c>
+      <c r="CI48" s="11">
+        <f t="shared" si="25"/>
+        <v>1.4451510333863276</v>
+      </c>
       <c r="CK48" s="14"/>
       <c r="CL48" s="13"/>
       <c r="CN48" s="12"/>
@@ -11382,7 +12231,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -11394,10 +12243,27 @@
         <v>-0.50517615176157249</v>
       </c>
       <c r="CC49" s="14"/>
-      <c r="CD49" s="13"/>
-      <c r="CF49" s="12"/>
-      <c r="CH49" s="12"/>
-      <c r="CI49" s="11"/>
+      <c r="CD49" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE49" s="10">
+        <v>8</v>
+      </c>
+      <c r="CF49" s="12">
+        <v>227482.85714284002</v>
+      </c>
+      <c r="CG49" s="10">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="CH49" s="12">
+        <f t="shared" si="24"/>
+        <v>175314.28571428003</v>
+      </c>
+      <c r="CI49" s="11">
+        <f t="shared" si="25"/>
+        <v>3.3605345309168881</v>
+      </c>
       <c r="CK49" s="14"/>
       <c r="CL49" s="13"/>
       <c r="CN49" s="12"/>
@@ -11609,7 +12475,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -11621,10 +12487,27 @@
         <v>-0.33999246136449529</v>
       </c>
       <c r="CC50" s="14"/>
-      <c r="CD50" s="13"/>
-      <c r="CF50" s="12"/>
-      <c r="CH50" s="12"/>
-      <c r="CI50" s="11"/>
+      <c r="CD50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE50" s="10">
+        <v>14</v>
+      </c>
+      <c r="CF50" s="12">
+        <v>210761.90476186998</v>
+      </c>
+      <c r="CG50" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH50" s="12">
+        <f t="shared" si="24"/>
+        <v>43999.999999989988</v>
+      </c>
+      <c r="CI50" s="11">
+        <f t="shared" si="25"/>
+        <v>0.26384922901197227</v>
+      </c>
       <c r="CK50" s="14"/>
       <c r="CL50" s="13"/>
       <c r="CN50" s="12"/>
@@ -11836,7 +12719,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -11848,10 +12731,27 @@
         <v>-0.50697438498605774</v>
       </c>
       <c r="CC51" s="14"/>
-      <c r="CD51" s="13"/>
-      <c r="CF51" s="12"/>
-      <c r="CH51" s="12"/>
-      <c r="CI51" s="11"/>
+      <c r="CD51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE51" s="10">
+        <v>32</v>
+      </c>
+      <c r="CF51" s="12">
+        <v>1105523.8095237699</v>
+      </c>
+      <c r="CG51" s="10">
+        <f t="shared" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="CH51" s="12">
+        <f t="shared" si="24"/>
+        <v>735238.09523806989</v>
+      </c>
+      <c r="CI51" s="11">
+        <f t="shared" si="25"/>
+        <v>1.9855967078189383</v>
+      </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13"/>
       <c r="CN51" s="12"/>
@@ -12064,7 +12964,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -12075,13 +12975,28 @@
         <f t="shared" si="22"/>
         <v>-0.35368091226180448</v>
       </c>
-      <c r="CC52" s="9"/>
+      <c r="CC52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CD52" s="9"/>
-      <c r="CE52" s="8"/>
-      <c r="CF52" s="7"/>
-      <c r="CG52" s="27"/>
-      <c r="CH52" s="28"/>
-      <c r="CI52" s="29"/>
+      <c r="CE52" s="8">
+        <v>291</v>
+      </c>
+      <c r="CF52" s="7">
+        <v>2059051.4285707299</v>
+      </c>
+      <c r="CG52" s="27">
+        <f t="shared" si="23"/>
+        <v>79</v>
+      </c>
+      <c r="CH52" s="28">
+        <f t="shared" si="24"/>
+        <v>1086828.0952379201</v>
+      </c>
+      <c r="CI52" s="29">
+        <f t="shared" si="25"/>
+        <v>1.1178790489549779</v>
+      </c>
       <c r="CK52" s="9"/>
       <c r="CL52" s="9"/>
       <c r="CM52" s="8"/>
@@ -12269,7 +13184,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -12280,13 +13195,26 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC53" s="14"/>
-      <c r="CD53" s="32"/>
+      <c r="CC53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CD53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CE53" s="15"/>
       <c r="CF53" s="33"/>
-      <c r="CG53" s="10"/>
-      <c r="CH53" s="12"/>
-      <c r="CI53" s="11"/>
+      <c r="CG53" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH53" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI53" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK53" s="14"/>
       <c r="CL53" s="32"/>
       <c r="CM53" s="15"/>
@@ -12482,7 +13410,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -12494,12 +13422,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC54" s="14"/>
-      <c r="CD54" s="32"/>
+      <c r="CD54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE54" s="15"/>
       <c r="CF54" s="33"/>
-      <c r="CG54" s="10"/>
-      <c r="CH54" s="12"/>
-      <c r="CI54" s="11"/>
+      <c r="CG54" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH54" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI54" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK54" s="14"/>
       <c r="CL54" s="32"/>
       <c r="CM54" s="15"/>
@@ -12715,7 +13654,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -12727,10 +13666,27 @@
         <v>-0.28492376209290476</v>
       </c>
       <c r="CC55" s="14"/>
-      <c r="CD55" s="13"/>
-      <c r="CF55" s="12"/>
-      <c r="CH55" s="12"/>
-      <c r="CI55" s="11"/>
+      <c r="CD55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE55" s="10">
+        <v>114</v>
+      </c>
+      <c r="CF55" s="12">
+        <v>112772.38095190004</v>
+      </c>
+      <c r="CG55" s="10">
+        <f t="shared" si="23"/>
+        <v>-4</v>
+      </c>
+      <c r="CH55" s="12">
+        <f t="shared" si="24"/>
+        <v>10624.761904769985</v>
+      </c>
+      <c r="CI55" s="11">
+        <f t="shared" si="25"/>
+        <v>0.10401379889107165</v>
+      </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13"/>
       <c r="CN55" s="12"/>
@@ -12942,7 +13898,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -12954,10 +13910,27 @@
         <v>1.3282677695419092E-2</v>
       </c>
       <c r="CC56" s="14"/>
-      <c r="CD56" s="13"/>
-      <c r="CF56" s="12"/>
-      <c r="CH56" s="12"/>
-      <c r="CI56" s="11"/>
+      <c r="CD56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE56" s="10">
+        <v>68</v>
+      </c>
+      <c r="CF56" s="12">
+        <v>77828.571428499999</v>
+      </c>
+      <c r="CG56" s="10">
+        <f t="shared" si="23"/>
+        <v>-21</v>
+      </c>
+      <c r="CH56" s="12">
+        <f t="shared" si="24"/>
+        <v>-22505.714285690003</v>
+      </c>
+      <c r="CI56" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.22430731554514952</v>
+      </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13"/>
       <c r="CN56" s="12"/>
@@ -13169,7 +14142,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -13181,10 +14154,27 @@
         <v>-0.21089097572150597</v>
       </c>
       <c r="CC57" s="14"/>
-      <c r="CD57" s="13"/>
-      <c r="CF57" s="12"/>
-      <c r="CH57" s="12"/>
-      <c r="CI57" s="11"/>
+      <c r="CD57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE57" s="10">
+        <v>26</v>
+      </c>
+      <c r="CF57" s="12">
+        <v>161180.95238094003</v>
+      </c>
+      <c r="CG57" s="10">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="CH57" s="12">
+        <f t="shared" si="24"/>
+        <v>29933.333333340008</v>
+      </c>
+      <c r="CI57" s="11">
+        <f t="shared" si="25"/>
+        <v>0.22806762934483393</v>
+      </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13"/>
       <c r="CN57" s="12"/>
@@ -13396,7 +14386,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -13408,10 +14398,27 @@
         <v>-0.76402116402122544</v>
       </c>
       <c r="CC58" s="14"/>
-      <c r="CD58" s="13"/>
-      <c r="CF58" s="12"/>
-      <c r="CH58" s="12"/>
-      <c r="CI58" s="11"/>
+      <c r="CD58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE58" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF58" s="12">
+        <v>97714.28571425</v>
+      </c>
+      <c r="CG58" s="10">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="CH58" s="12">
+        <f t="shared" si="24"/>
+        <v>55238.095238080001</v>
+      </c>
+      <c r="CI58" s="11">
+        <f t="shared" si="25"/>
+        <v>1.3004484304935418</v>
+      </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13"/>
       <c r="CN58" s="12"/>
@@ -13598,7 +14605,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -13610,10 +14617,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC59" s="14"/>
-      <c r="CD59" s="13"/>
+      <c r="CD59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF59" s="12"/>
-      <c r="CH59" s="12"/>
-      <c r="CI59" s="11"/>
+      <c r="CG59" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH59" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI59" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK59" s="14"/>
       <c r="CL59" s="13"/>
       <c r="CN59" s="12"/>
@@ -13820,7 +14839,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -13832,10 +14851,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC60" s="14"/>
-      <c r="CD60" s="13"/>
-      <c r="CF60" s="12"/>
-      <c r="CH60" s="12"/>
-      <c r="CI60" s="11"/>
+      <c r="CD60" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE60" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF60" s="12">
+        <v>8780</v>
+      </c>
+      <c r="CG60" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH60" s="12">
+        <f t="shared" si="24"/>
+        <v>2490</v>
+      </c>
+      <c r="CI60" s="11">
+        <f t="shared" si="25"/>
+        <v>0.3958664546899841</v>
+      </c>
       <c r="CK60" s="14"/>
       <c r="CL60" s="13"/>
       <c r="CN60" s="12"/>
@@ -14047,7 +15083,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -14059,10 +15095,27 @@
         <v>-0.65357142857144235</v>
       </c>
       <c r="CC61" s="14"/>
-      <c r="CD61" s="13"/>
-      <c r="CF61" s="12"/>
-      <c r="CH61" s="12"/>
-      <c r="CI61" s="11"/>
+      <c r="CD61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE61" s="10">
+        <v>3</v>
+      </c>
+      <c r="CF61" s="12">
+        <v>91142.857142840003</v>
+      </c>
+      <c r="CG61" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH61" s="12">
+        <f t="shared" si="24"/>
+        <v>8000</v>
+      </c>
+      <c r="CI61" s="11">
+        <f t="shared" si="25"/>
+        <v>9.62199312714975E-2</v>
+      </c>
       <c r="CK61" s="14"/>
       <c r="CL61" s="13"/>
       <c r="CN61" s="12"/>
@@ -14274,7 +15327,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -14286,10 +15339,27 @@
         <v>-0.19971919971913504</v>
       </c>
       <c r="CC62" s="14"/>
-      <c r="CD62" s="13"/>
-      <c r="CF62" s="12"/>
-      <c r="CH62" s="12"/>
-      <c r="CI62" s="11"/>
+      <c r="CD62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE62" s="10">
+        <v>29</v>
+      </c>
+      <c r="CF62" s="12">
+        <v>380761.90476187004</v>
+      </c>
+      <c r="CG62" s="10">
+        <f t="shared" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="CH62" s="12">
+        <f t="shared" si="24"/>
+        <v>163619.04761903003</v>
+      </c>
+      <c r="CI62" s="11">
+        <f t="shared" si="25"/>
+        <v>0.75350877192980292</v>
+      </c>
       <c r="CK62" s="14"/>
       <c r="CL62" s="13"/>
       <c r="CN62" s="12"/>
@@ -14501,7 +15571,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -14513,10 +15583,27 @@
         <v>-0.36087127603525215</v>
       </c>
       <c r="CC63" s="14"/>
-      <c r="CD63" s="13"/>
-      <c r="CF63" s="12"/>
-      <c r="CH63" s="12"/>
-      <c r="CI63" s="11"/>
+      <c r="CD63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE63" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF63" s="12">
+        <v>585904.76190473</v>
+      </c>
+      <c r="CG63" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH63" s="12">
+        <f t="shared" si="24"/>
+        <v>129563.80952379992</v>
+      </c>
+      <c r="CI63" s="11">
+        <f t="shared" si="25"/>
+        <v>0.28391887435876384</v>
+      </c>
       <c r="CK63" s="14"/>
       <c r="CL63" s="13"/>
       <c r="CN63" s="12"/>
@@ -14729,7 +15816,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -14740,13 +15827,28 @@
         <f t="shared" si="22"/>
         <v>-0.371875469355818</v>
       </c>
-      <c r="CC64" s="9"/>
+      <c r="CC64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CD64" s="9"/>
-      <c r="CE64" s="8"/>
-      <c r="CF64" s="7"/>
-      <c r="CG64" s="27"/>
-      <c r="CH64" s="28"/>
-      <c r="CI64" s="29"/>
+      <c r="CE64" s="8">
+        <v>269</v>
+      </c>
+      <c r="CF64" s="7">
+        <v>1516085.71428503</v>
+      </c>
+      <c r="CG64" s="27">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="CH64" s="28">
+        <f t="shared" si="24"/>
+        <v>376963.33333332976</v>
+      </c>
+      <c r="CI64" s="29">
+        <f t="shared" si="25"/>
+        <v>0.33092434986519093</v>
+      </c>
       <c r="CK64" s="9"/>
       <c r="CL64" s="9"/>
       <c r="CM64" s="8"/>
@@ -14963,7 +16065,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -14974,13 +16076,28 @@
         <f t="shared" si="22"/>
         <v>-0.34719833949510465</v>
       </c>
-      <c r="CC65" s="4"/>
+      <c r="CC65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CD65" s="4"/>
-      <c r="CE65" s="3"/>
-      <c r="CF65" s="2"/>
-      <c r="CG65" s="6"/>
-      <c r="CH65" s="5"/>
-      <c r="CI65" s="30"/>
+      <c r="CE65" s="3">
+        <v>2305</v>
+      </c>
+      <c r="CF65" s="2">
+        <v>21361582.380947892</v>
+      </c>
+      <c r="CG65" s="6">
+        <f t="shared" si="23"/>
+        <v>412</v>
+      </c>
+      <c r="CH65" s="5">
+        <f t="shared" si="24"/>
+        <v>10239397.619047023</v>
+      </c>
+      <c r="CI65" s="30">
+        <f t="shared" si="25"/>
+        <v>0.92062826128569275</v>
+      </c>
       <c r="CK65" s="4"/>
       <c r="CL65" s="4"/>
       <c r="CM65" s="3"/>
@@ -15004,7 +16121,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15016,7 +16133,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15028,7 +16145,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15040,7 +16157,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15052,7 +16169,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15064,7 +16181,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15076,7 +16193,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15088,7 +16205,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15100,7 +16217,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15112,7 +16229,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15124,19 +16241,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{DDBF6E41-C389-2344-92BB-6A5E3B3BC008}">
-            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>CG5:CI65</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15148,7 +16253,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15159,6 +16264,18 @@
           </x14:cfRule>
           <xm:sqref>CW5:CY65</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>CG5:CI65</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
